--- a/output/pdf_financials_xlsx/YRB.xlsx
+++ b/output/pdf_financials_xlsx/YRB.xlsx
@@ -1079,28 +1079,28 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.00617</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.003515</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-1e-05</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.006596</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.011748</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.001068</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-2.7e-05</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000152</v>
       </c>
       <c r="L12" s="1" t="inlineStr">
         <is>
@@ -1117,10 +1117,10 @@
         <v>0</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.06433800000000001</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.974976</v>
       </c>
     </row>
     <row r="13">
@@ -2030,22 +2030,22 @@
         <v>-1.650044</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.138042</v>
+        <v>-1.144212</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.014648</v>
+        <v>-1.011133</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.204758</v>
+        <v>-1.204748</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.519799</v>
+        <v>-1.513203</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.60141</v>
+        <v>-0.589662</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.547556</v>
+        <v>-0.546488</v>
       </c>
       <c r="J27" s="1" t="inlineStr">
         <is>
@@ -2072,10 +2072,10 @@
         <v>-2.436538</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>8.020395000000001</v>
+        <v>7.956057</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>0.221732</v>
+        <v>-0.753244</v>
       </c>
     </row>
     <row r="28">
@@ -2148,22 +2148,22 @@
         <v>-1.650044</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.138042</v>
+        <v>-1.144212</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.014648</v>
+        <v>-1.011133</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.204758</v>
+        <v>-1.204748</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.519799</v>
+        <v>-1.513203</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.60141</v>
+        <v>-0.589662</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.547556</v>
+        <v>-0.546488</v>
       </c>
       <c r="J29" s="1" t="inlineStr">
         <is>
@@ -2190,10 +2190,10 @@
         <v>-2.436538</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>8.020395000000001</v>
+        <v>7.956057</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>0.221732</v>
+        <v>-0.753244</v>
       </c>
     </row>
     <row r="30">
@@ -2223,16 +2223,16 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-1657.642510216156</v>
+        <v>-1657.628751083532</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-1275.694800016788</v>
+        <v>-1270.158223863684</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-144.9938883705456</v>
+        <v>-142.1615639985245</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-81.36712509937662</v>
+        <v>-81.20841970740551</v>
       </c>
       <c r="J30" s="1" t="inlineStr">
         <is>
@@ -2464,19 +2464,19 @@
         </is>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>1.886476</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.376012</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.222759</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.233207</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.428654</v>
       </c>
     </row>
     <row r="35">
@@ -2578,19 +2578,19 @@
         </is>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>1.886476</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.376012</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.015</v>
+        <v>0.237759</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.015</v>
+        <v>0.248207</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0.0825</v>
+        <v>0.511154</v>
       </c>
     </row>
     <row r="37">
@@ -3262,19 +3262,19 @@
         </is>
       </c>
       <c r="M48" s="3" t="n">
-        <v>1.948983</v>
+        <v>0.06250699999999999</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.545275</v>
+        <v>0.169263</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.273759</v>
+        <v>0.051</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>3.588839</v>
+        <v>3.355632</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>10.140066</v>
+        <v>9.711411999999999</v>
       </c>
     </row>
     <row r="49">
@@ -7758,19 +7758,19 @@
         </is>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.019177</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.0203</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.019039</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-0.004103</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>0</v>
+        <v>-0.020523</v>
       </c>
     </row>
     <row r="125">
@@ -7819,19 +7819,19 @@
         </is>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.019177</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.0203</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-0.019039</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-0.004103</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>0</v>
+        <v>-0.020523</v>
       </c>
     </row>
     <row r="126">
@@ -8618,7 +8618,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -10964,7 +10964,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -14026,7 +14026,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -24686,7 +24686,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr"/>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E172" t="inlineStr">
         <is>
           <t>-</t>
@@ -27152,7 +27156,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr"/>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E198" t="inlineStr">
         <is>
           <t>-</t>
@@ -29728,7 +29736,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr"/>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E225" t="inlineStr">
         <is>
           <t>-</t>
@@ -31620,7 +31632,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr"/>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E245" t="inlineStr">
         <is>
           <t>-</t>
@@ -40296,7 +40312,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
@@ -44522,7 +44538,7 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
@@ -44620,7 +44636,7 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
@@ -45834,7 +45850,7 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
@@ -45932,7 +45948,7 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
@@ -46030,7 +46046,7 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
@@ -46974,7 +46990,7 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
@@ -47064,7 +47080,7 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
@@ -47902,7 +47918,7 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
@@ -48570,7 +48586,7 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
@@ -50834,7 +50850,7 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E447" t="inlineStr">

--- a/output/pdf_financials_xlsx/YRB.xlsx
+++ b/output/pdf_financials_xlsx/YRB.xlsx
@@ -595,15 +595,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K4" s="3" t="n">
+        <v>0.000369</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>0.000278</v>
       </c>
       <c r="M4" s="1" t="inlineStr">
         <is>
@@ -667,10 +663,8 @@
       <c r="K5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M5" s="3" t="n">
         <v>0.745514</v>
@@ -731,15 +725,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K6" s="3" t="n">
+        <v>0.000369</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>0.000278</v>
       </c>
       <c r="M6" s="1" t="inlineStr">
         <is>
@@ -803,10 +793,8 @@
       <c r="K7" s="3" t="n">
         <v>0.00575</v>
       </c>
-      <c r="L7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L7" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M7" s="3" t="n">
         <v>0.06948799999999999</v>
@@ -860,10 +848,8 @@
       <c r="K8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M8" s="3" t="n">
         <v>0</v>
@@ -917,10 +903,8 @@
       <c r="K9" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L9" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M9" s="3" t="n">
         <v>0</v>
@@ -974,10 +958,8 @@
       <c r="K10" s="3" t="n">
         <v>0.00575</v>
       </c>
-      <c r="L10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L10" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M10" s="3" t="n">
         <v>0.06948799999999999</v>
@@ -1038,15 +1020,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K11" s="3" t="n">
+        <v>-0.005381</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>0.000278</v>
       </c>
       <c r="M11" s="1" t="inlineStr">
         <is>
@@ -1102,10 +1080,8 @@
       <c r="K12" s="3" t="n">
         <v>-0.000152</v>
       </c>
-      <c r="L12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L12" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>0</v>
@@ -1159,10 +1135,8 @@
       <c r="K13" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="L13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L13" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="M13" s="3" t="n">
         <v>-0</v>
@@ -1216,10 +1190,8 @@
       <c r="K14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M14" s="3" t="n">
         <v>0</v>
@@ -1273,10 +1245,8 @@
       <c r="K15" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L15" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M15" s="3" t="n">
         <v>0</v>
@@ -1391,10 +1361,8 @@
       <c r="K17" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="L17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L17" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="M17" s="3" t="n">
         <v>-0</v>
@@ -1683,10 +1651,8 @@
       <c r="K21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M21" s="3" t="n">
         <v>0</v>
@@ -1740,10 +1706,8 @@
       <c r="K22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>0</v>
@@ -2103,21 +2067,19 @@
         <v>0</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0</v>
+        <v>0.010043</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>0.010554</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0</v>
+        <v>0.010956</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.010955</v>
+      </c>
+      <c r="L28" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M28" s="3" t="n">
         <v>0.027885</v>
@@ -2126,13 +2088,13 @@
         <v>0.028903</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0</v>
+        <v>0.02681</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0</v>
+        <v>0.011405</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>0</v>
+        <v>0.021646</v>
       </c>
     </row>
     <row r="29">
@@ -2160,10 +2122,10 @@
         <v>-1.513203</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.589662</v>
+        <v>-0.579619</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.546488</v>
+        <v>-0.535934</v>
       </c>
       <c r="J29" s="1" t="inlineStr">
         <is>
@@ -2187,13 +2149,13 @@
         <v>-2.474907</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-2.436538</v>
+        <v>-2.409728</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>7.956057</v>
+        <v>7.967462</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-0.753244</v>
+        <v>-0.731598</v>
       </c>
     </row>
     <row r="30">
@@ -2229,10 +2191,10 @@
         <v>-1270.158223863684</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-142.1615639985245</v>
+        <v>-139.7402979389223</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-81.20841970740551</v>
+        <v>-79.64008945753368</v>
       </c>
       <c r="J30" s="1" t="inlineStr">
         <is>
@@ -4400,10 +4362,10 @@
         <v>0</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>0.034297</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>0.034276</v>
       </c>
     </row>
     <row r="68">
@@ -4457,10 +4419,10 @@
         <v>0.152129</v>
       </c>
       <c r="P68" s="3" t="n">
-        <v>0.277188</v>
+        <v>0.311485</v>
       </c>
       <c r="Q68" s="3" t="n">
-        <v>0.213629</v>
+        <v>0.247905</v>
       </c>
     </row>
     <row r="69">
@@ -4562,13 +4524,13 @@
         </is>
       </c>
       <c r="M70" s="3" t="n">
-        <v>0</v>
+        <v>0.017716</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>0</v>
+        <v>0.017242</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>0</v>
+        <v>0.0005419999999999999</v>
       </c>
       <c r="P70" s="3" t="n">
         <v>0.018611</v>
@@ -4619,13 +4581,13 @@
         </is>
       </c>
       <c r="M71" s="3" t="n">
-        <v>0</v>
+        <v>0.017716</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0</v>
+        <v>0.017242</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>0</v>
+        <v>0.0005419999999999999</v>
       </c>
       <c r="P71" s="3" t="n">
         <v>0.018611</v>
@@ -4847,19 +4809,19 @@
         </is>
       </c>
       <c r="M75" s="3" t="n">
-        <v>0.197273</v>
+        <v>0.179557</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>0.066746</v>
+        <v>0.049504</v>
       </c>
       <c r="O75" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>0.2672</v>
+        <v>0.232903</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>0.249408</v>
+        <v>0.215132</v>
       </c>
     </row>
     <row r="76">
@@ -5158,15 +5120,13 @@
         </is>
       </c>
       <c r="M80" s="3" t="n">
-        <v>0.0006477583205838392</v>
+        <v>0.001293039832474488</v>
       </c>
       <c r="N80" s="3" t="n">
-        <v>2.089066703668586e-05</v>
-      </c>
-      <c r="O80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.0006854605582664601</v>
+      </c>
+      <c r="O80" s="3" t="n">
+        <v>2.223873030800436e-05</v>
       </c>
       <c r="P80" s="3" t="n">
         <v>0.0005624910443754991</v>
@@ -6271,16 +6231,16 @@
         <v>0</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>0.010043</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.010554</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>0.010956</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.010955</v>
       </c>
       <c r="L100" s="1" t="inlineStr">
         <is>
@@ -6291,16 +6251,16 @@
         <v>0</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>0.028903</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>0.02681</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>0.011405</v>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0</v>
+        <v>0.021646</v>
       </c>
     </row>
     <row r="101">
@@ -8489,7 +8449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T469"/>
+  <dimension ref="A1:T485"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -13364,7 +13324,11 @@
           <t>Lease liabilities (note 20)</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
@@ -14608,7 +14572,11 @@
           <t>Lease liabilities (note 21)</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>-</t>
@@ -23724,7 +23692,11 @@
           <t>Amortization expense (notes 13 and 14)</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr"/>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr">
         <is>
           <t>-</t>
@@ -26192,7 +26164,11 @@
           <t>Amortization expense (notes 15 and 16)</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr"/>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E188" t="inlineStr">
         <is>
           <t>-</t>
@@ -28504,7 +28480,11 @@
           <t>Amortization expense (notes 15 and 16)</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr"/>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E212" t="inlineStr">
         <is>
           <t>-</t>
@@ -32682,7 +32662,11 @@
           <t>Amortization expense (note 16)</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr"/>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E256" t="inlineStr">
         <is>
           <t>-</t>
@@ -34288,7 +34272,11 @@
           <t>Amortization expense (note 17)</t>
         </is>
       </c>
-      <c r="D273" t="inlineStr"/>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E273" t="inlineStr">
         <is>
           <t>-</t>
@@ -35996,7 +35984,11 @@
           <t>Amortization expense (note 11)</t>
         </is>
       </c>
-      <c r="D291" t="inlineStr"/>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E291" t="inlineStr">
         <is>
           <t>-</t>
@@ -38118,7 +38110,11 @@
           <t>Future income taxes</t>
         </is>
       </c>
-      <c r="D313" t="inlineStr"/>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E313" t="inlineStr">
         <is>
           <t>-</t>
@@ -45018,19 +45014,15 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Contract revenue                                     $      17,463   $         −</t>
+          <t>Revenus</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Management fees</t>
-        </is>
-      </c>
-      <c r="D385" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Produits des contrats 776 041 $</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr"/>
       <c r="E385" t="inlineStr">
         <is>
           <t>-</t>
@@ -45071,16 +45063,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M385" s="5" t="n">
-        <v>0.043928</v>
+      <c r="M385" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N385" s="5" t="n">
-        <v>0.00575</v>
-      </c>
-      <c r="O385" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.000463</v>
+      </c>
+      <c r="O385" s="5" t="n">
+        <v>1.7e-05</v>
       </c>
       <c r="P385" t="inlineStr">
         <is>
@@ -45116,12 +45108,12 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Contract revenue                                     $      17,463   $         −</t>
+          <t>Revenus</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Rental of facilities</t>
+          <t>Frais de gestion –</t>
         </is>
       </c>
       <c r="D386" t="inlineStr"/>
@@ -45165,16 +45157,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M386" s="5" t="n">
-        <v>0.1306</v>
+      <c r="M386" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N386" s="5" t="n">
-        <v>0.032811</v>
-      </c>
-      <c r="O386" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.00075</v>
+      </c>
+      <c r="O386" s="5" t="n">
+        <v>5e-06</v>
       </c>
       <c r="P386" t="inlineStr">
         <is>
@@ -45210,12 +45202,12 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Ellison Royalty)                                      −          2,250,000</t>
+          <t>Revenus</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Revenue related to flow-through shares</t>
+          <t>Location de locaux 31 078</t>
         </is>
       </c>
       <c r="D387" t="inlineStr"/>
@@ -45259,16 +45251,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M387" s="5" t="n">
-        <v>0.476181</v>
+      <c r="M387" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N387" s="5" t="n">
-        <v>0.222345</v>
-      </c>
-      <c r="O387" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.000811</v>
+      </c>
+      <c r="O387" s="5" t="n">
+        <v>3.2e-05</v>
       </c>
       <c r="P387" t="inlineStr">
         <is>
@@ -45304,12 +45296,12 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Ellison Royalty)                                      −          2,250,000</t>
+          <t>Revenus</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Ellison Royalty)                                      −          2,250,000 total</t>
+          <t>Autres revenus provenant de l'émission d'actions accréditives 571 773</t>
         </is>
       </c>
       <c r="D388" t="inlineStr"/>
@@ -45353,16 +45345,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M388" s="5" t="n">
-        <v>2.900709</v>
+      <c r="M388" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N388" s="5" t="n">
-        <v>0.278369</v>
-      </c>
-      <c r="O388" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.000345</v>
+      </c>
+      <c r="O388" s="5" t="n">
+        <v>0.000222</v>
       </c>
       <c r="P388" t="inlineStr">
         <is>
@@ -45398,15 +45390,19 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Revenus</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Administrative charges (note 15)</t>
-        </is>
-      </c>
-      <c r="D389" t="inlineStr"/>
+          <t>Revenus total</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
       <c r="E389" t="inlineStr">
         <is>
           <t>-</t>
@@ -45447,16 +45443,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M389" s="5" t="n">
-        <v>0.84922</v>
+      <c r="M389" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N389" s="5" t="n">
-        <v>1.016408</v>
-      </c>
-      <c r="O389" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.000369</v>
+      </c>
+      <c r="O389" s="5" t="n">
+        <v>0.000278</v>
       </c>
       <c r="P389" t="inlineStr">
         <is>
@@ -45492,12 +45488,12 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Charges</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Share-based payments</t>
+          <t>Coûts des ventes 703</t>
         </is>
       </c>
       <c r="D390" t="inlineStr"/>
@@ -45511,34 +45507,48 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G390" s="5" t="n">
-        <v>0.139573</v>
-      </c>
-      <c r="H390" s="5" t="n">
-        <v>0.299926</v>
-      </c>
-      <c r="I390" s="5" t="n">
-        <v>0.265975</v>
-      </c>
-      <c r="J390" s="5" t="n">
-        <v>0.271595</v>
-      </c>
-      <c r="K390" s="5" t="n">
-        <v>0.103422</v>
-      </c>
-      <c r="L390" s="5" t="n">
-        <v>0.039773</v>
-      </c>
-      <c r="M390" s="5" t="n">
-        <v>0.0007</v>
-      </c>
-      <c r="N390" s="5" t="n">
-        <v>0.0338</v>
-      </c>
-      <c r="O390" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J390" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L390" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M390" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N390" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O390" s="5" t="n">
+        <v>0.000267</v>
       </c>
       <c r="P390" t="inlineStr">
         <is>
@@ -45574,49 +45584,65 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Charges</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Property maintenance</t>
+          <t>Charges administratives (note 15) 977 393 1</t>
         </is>
       </c>
       <c r="D391" t="inlineStr"/>
-      <c r="E391" s="5" t="n">
-        <v>0.011336</v>
-      </c>
-      <c r="F391" s="5" t="n">
-        <v>0.021222</v>
-      </c>
-      <c r="G391" s="5" t="n">
-        <v>0.008083</v>
-      </c>
-      <c r="H391" s="5" t="n">
-        <v>0.004798</v>
-      </c>
-      <c r="I391" s="5" t="n">
-        <v>0.003848</v>
-      </c>
-      <c r="J391" s="5" t="n">
-        <v>0.049878</v>
-      </c>
-      <c r="K391" s="5" t="n">
-        <v>0.122423</v>
-      </c>
-      <c r="L391" s="5" t="n">
-        <v>0.134557</v>
-      </c>
-      <c r="M391" s="5" t="n">
-        <v>0.167231</v>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J391" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L391" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M391" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N391" s="5" t="n">
-        <v>0.171542</v>
-      </c>
-      <c r="O391" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.000408</v>
+      </c>
+      <c r="O391" s="5" t="n">
+        <v>1.6e-05</v>
       </c>
       <c r="P391" t="inlineStr">
         <is>
@@ -45652,12 +45678,12 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Charges</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Chibougamau building expenses (note 16)</t>
+          <t>Paiements fondés sur des actions 53 010</t>
         </is>
       </c>
       <c r="D392" t="inlineStr"/>
@@ -45701,16 +45727,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M392" s="5" t="n">
-        <v>0.030412</v>
+      <c r="M392" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N392" s="5" t="n">
-        <v>0.033529</v>
-      </c>
-      <c r="O392" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.0008</v>
+      </c>
+      <c r="O392" s="5" t="n">
+        <v>3.3e-05</v>
       </c>
       <c r="P392" t="inlineStr">
         <is>
@@ -45746,12 +45772,12 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>and evaluation assets                                 −           129,463</t>
+          <t>Charges</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>and evaluation assets                                 −           129,463 total</t>
+          <t>Frais de gestion des propriétés minières 124 514</t>
         </is>
       </c>
       <c r="D393" t="inlineStr"/>
@@ -45795,16 +45821,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M393" s="5" t="n">
-        <v>1.177026</v>
+      <c r="M393" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N393" s="5" t="n">
-        <v>1.255279</v>
-      </c>
-      <c r="O393" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.0005419999999999999</v>
+      </c>
+      <c r="O393" s="5" t="n">
+        <v>0.000171</v>
       </c>
       <c r="P393" t="inlineStr">
         <is>
@@ -45840,19 +45866,15 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>and evaluation assets                                 −           129,463</t>
+          <t>Charges</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D394" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>Dépenses de l’édifice de Chibougamau (note 16) 31 350</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr"/>
       <c r="E394" t="inlineStr">
         <is>
           <t>-</t>
@@ -45893,16 +45915,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M394" s="5" t="n">
-        <v>-2.7e-05</v>
+      <c r="M394" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N394" s="5" t="n">
-        <v>-0.000152</v>
-      </c>
-      <c r="O394" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.000529</v>
+      </c>
+      <c r="O394" s="5" t="n">
+        <v>3.3e-05</v>
       </c>
       <c r="P394" t="inlineStr">
         <is>
@@ -45938,19 +45960,15 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>and evaluation assets                                 −           129,463</t>
+          <t>Charges</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Interest expense</t>
-        </is>
-      </c>
-      <c r="D395" t="inlineStr">
-        <is>
-          <t>InterestExpenseOperating</t>
-        </is>
-      </c>
+          <t>Charges total</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr"/>
       <c r="E395" t="inlineStr">
         <is>
           <t>-</t>
@@ -45991,16 +46009,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M395" s="5" t="n">
-        <v>0.003156</v>
+      <c r="M395" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N395" s="5" t="n">
-        <v>0.027519</v>
-      </c>
-      <c r="O395" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.000279</v>
+      </c>
+      <c r="O395" s="5" t="n">
+        <v>0.000255</v>
       </c>
       <c r="P395" t="inlineStr">
         <is>
@@ -46036,19 +46054,15 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>and evaluation assets                                 −           129,463</t>
+          <t>Charges</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Net interest expense</t>
-        </is>
-      </c>
-      <c r="D396" t="inlineStr">
-        <is>
-          <t>InterestExpenseOperating</t>
-        </is>
-      </c>
+          <t>Revenus d’intérêts</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr"/>
       <c r="E396" t="inlineStr">
         <is>
           <t>-</t>
@@ -46089,11 +46103,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M396" s="5" t="n">
-        <v>0.003129</v>
+      <c r="M396" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N396" s="5" t="n">
-        <v>0.027367</v>
+        <v>-0.000152</v>
       </c>
       <c r="O396" t="inlineStr">
         <is>
@@ -46134,12 +46150,12 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>and evaluation assets                                 −           129,463</t>
+          <t>Charges</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Net (loss) income and comprehensive (loss) income $</t>
+          <t>Charges d’intérêts 4 270</t>
         </is>
       </c>
       <c r="D397" t="inlineStr"/>
@@ -46183,16 +46199,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M397" s="5" t="n">
-        <v>1.720554</v>
+      <c r="M397" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N397" s="5" t="n">
-        <v>-1.004277</v>
-      </c>
-      <c r="O397" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.000519</v>
+      </c>
+      <c r="O397" s="5" t="n">
+        <v>2.7e-05</v>
       </c>
       <c r="P397" t="inlineStr">
         <is>
@@ -46228,19 +46244,15 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>and evaluation assets                                 −           129,463</t>
+          <t>Charges</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Net (loss) earnings per share, basic and diluted $</t>
-        </is>
-      </c>
-      <c r="D398" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Charges d’intérêts nettes 4 270</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr"/>
       <c r="E398" t="inlineStr">
         <is>
           <t>-</t>
@@ -46281,16 +46293,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M398" s="5" t="n">
-        <v>1e-08</v>
+      <c r="M398" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N398" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="O398" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.000367</v>
+      </c>
+      <c r="O398" s="5" t="n">
+        <v>2.7e-05</v>
       </c>
       <c r="P398" t="inlineStr">
         <is>
@@ -46326,19 +46338,15 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>and evaluation assets                                 −           129,463</t>
+          <t>Charges</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding</t>
-        </is>
-      </c>
-      <c r="D399" t="inlineStr">
-        <is>
-          <t>BasicAverageShares</t>
-        </is>
-      </c>
+          <t>Perte nette et résultat global (514 912) $ (1</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr"/>
       <c r="E399" t="inlineStr">
         <is>
           <t>-</t>
@@ -46379,16 +46387,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M399" s="5" t="n">
-        <v>300.631488</v>
+      <c r="M399" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N399" s="5" t="n">
-        <v>308.111917</v>
-      </c>
-      <c r="O399" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.000277</v>
+      </c>
+      <c r="O399" s="5" t="n">
+        <v>4e-06</v>
       </c>
       <c r="P399" t="inlineStr">
         <is>
@@ -46424,19 +46432,15 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Revenues</t>
+          <t>Charges</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Management fees $</t>
-        </is>
-      </c>
-      <c r="D400" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Moyenne pondérée du nombre d’actions en circulation 326 587 534 308</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr"/>
       <c r="E400" t="inlineStr">
         <is>
           <t>-</t>
@@ -46457,32 +46461,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I400" s="5" t="n">
-        <v>0.030679</v>
-      </c>
-      <c r="J400" s="5" t="n">
-        <v>0.087135</v>
-      </c>
-      <c r="K400" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="L400" s="5" t="n">
-        <v>0.040529</v>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J400" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L400" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M400" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N400" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O400" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N400" s="5" t="n">
+        <v>0.000917</v>
+      </c>
+      <c r="O400" s="5" t="n">
+        <v>0.000111</v>
       </c>
       <c r="P400" t="inlineStr">
         <is>
@@ -46518,15 +46526,19 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Revenues</t>
+          <t>Contract revenue                                     $      17,463   $         −</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Other revenue related to flow-through shares</t>
-        </is>
-      </c>
-      <c r="D401" t="inlineStr"/>
+          <t>Management fees</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E401" t="inlineStr">
         <is>
           <t>-</t>
@@ -46557,21 +46569,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K401" s="5" t="n">
-        <v>0.358193</v>
-      </c>
-      <c r="L401" s="5" t="n">
-        <v>0.579881</v>
-      </c>
-      <c r="M401" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N401" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L401" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M401" s="5" t="n">
+        <v>0.043928</v>
+      </c>
+      <c r="N401" s="5" t="n">
+        <v>0.00575</v>
       </c>
       <c r="O401" t="inlineStr">
         <is>
@@ -46612,19 +46624,15 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Revenues</t>
+          <t>Contract revenue                                     $      17,463   $         −</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Revenues total</t>
-        </is>
-      </c>
-      <c r="D402" t="inlineStr">
-        <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
+          <t>Rental of facilities</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr"/>
       <c r="E402" t="inlineStr">
         <is>
           <t>-</t>
@@ -46645,27 +46653,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I402" s="5" t="n">
-        <v>0.07267899999999999</v>
-      </c>
-      <c r="J402" s="5" t="n">
-        <v>0.119135</v>
-      </c>
-      <c r="K402" s="5" t="n">
-        <v>0.414783</v>
-      </c>
-      <c r="L402" s="5" t="n">
-        <v>0.672945</v>
-      </c>
-      <c r="M402" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N402" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J402" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L402" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M402" s="5" t="n">
+        <v>0.1306</v>
+      </c>
+      <c r="N402" s="5" t="n">
+        <v>0.032811</v>
       </c>
       <c r="O402" t="inlineStr">
         <is>
@@ -46706,12 +46718,12 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Ellison Royalty)                                      −          2,250,000</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Administrative charges (note 16)</t>
+          <t>Revenue related to flow-through shares</t>
         </is>
       </c>
       <c r="D403" t="inlineStr"/>
@@ -46745,21 +46757,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K403" s="5" t="n">
-        <v>0.773477</v>
-      </c>
-      <c r="L403" s="5" t="n">
-        <v>0.978755</v>
-      </c>
-      <c r="M403" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N403" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L403" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M403" s="5" t="n">
+        <v>0.476181</v>
+      </c>
+      <c r="N403" s="5" t="n">
+        <v>0.222345</v>
       </c>
       <c r="O403" t="inlineStr">
         <is>
@@ -46800,12 +46812,12 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Ellison Royalty)                                      −          2,250,000</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Chibougamau building expenses (note 17)</t>
+          <t>Ellison Royalty)                                      −          2,250,000 total</t>
         </is>
       </c>
       <c r="D404" t="inlineStr"/>
@@ -46839,21 +46851,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K404" s="5" t="n">
-        <v>0.028619</v>
-      </c>
-      <c r="L404" s="5" t="n">
-        <v>0.061895</v>
-      </c>
-      <c r="M404" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N404" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L404" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M404" s="5" t="n">
+        <v>2.900709</v>
+      </c>
+      <c r="N404" s="5" t="n">
+        <v>0.278369</v>
       </c>
       <c r="O404" t="inlineStr">
         <is>
@@ -46899,47 +46911,55 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Expenses total</t>
-        </is>
-      </c>
-      <c r="D405" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E405" s="5" t="n">
-        <v>2.108847</v>
-      </c>
-      <c r="F405" s="5" t="n">
-        <v>1.651232</v>
-      </c>
-      <c r="G405" s="5" t="n">
-        <v>1.144212</v>
-      </c>
-      <c r="H405" s="5" t="n">
-        <v>1.274451</v>
-      </c>
-      <c r="I405" s="5" t="n">
-        <v>1.211085</v>
-      </c>
-      <c r="J405" s="5" t="n">
-        <v>1.629801</v>
-      </c>
-      <c r="K405" s="5" t="n">
-        <v>1.027941</v>
-      </c>
-      <c r="L405" s="5" t="n">
-        <v>1.21498</v>
-      </c>
-      <c r="M405" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N405" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Administrative charges (note 15)</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr"/>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J405" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L405" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M405" s="5" t="n">
+        <v>0.84922</v>
+      </c>
+      <c r="N405" s="5" t="n">
+        <v>1.016408</v>
       </c>
       <c r="O405" t="inlineStr">
         <is>
@@ -46985,14 +47005,10 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D406" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>Share-based payments</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr"/>
       <c r="E406" t="inlineStr">
         <is>
           <t>-</t>
@@ -47004,32 +47020,28 @@
         </is>
       </c>
       <c r="G406" s="5" t="n">
-        <v>0.00617</v>
+        <v>0.139573</v>
       </c>
       <c r="H406" s="5" t="n">
-        <v>-0.003515</v>
+        <v>0.299926</v>
       </c>
       <c r="I406" s="5" t="n">
-        <v>-1e-05</v>
+        <v>0.265975</v>
       </c>
       <c r="J406" s="5" t="n">
-        <v>-0.006596</v>
+        <v>0.271595</v>
       </c>
       <c r="K406" s="5" t="n">
-        <v>-0.011748</v>
+        <v>0.103422</v>
       </c>
       <c r="L406" s="5" t="n">
-        <v>-0.001068</v>
-      </c>
-      <c r="M406" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N406" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.039773</v>
+      </c>
+      <c r="M406" s="5" t="n">
+        <v>0.0007</v>
+      </c>
+      <c r="N406" s="5" t="n">
+        <v>0.0338</v>
       </c>
       <c r="O406" t="inlineStr">
         <is>
@@ -47075,57 +47087,39 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Interest expense</t>
-        </is>
-      </c>
-      <c r="D407" t="inlineStr">
-        <is>
-          <t>InterestExpenseOperating</t>
-        </is>
-      </c>
-      <c r="E407" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F407" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G407" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H407" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Property maintenance</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr"/>
+      <c r="E407" s="5" t="n">
+        <v>0.011336</v>
+      </c>
+      <c r="F407" s="5" t="n">
+        <v>0.021222</v>
+      </c>
+      <c r="G407" s="5" t="n">
+        <v>0.008083</v>
+      </c>
+      <c r="H407" s="5" t="n">
+        <v>0.004798</v>
       </c>
       <c r="I407" s="5" t="n">
-        <v>0.066362</v>
+        <v>0.003848</v>
       </c>
       <c r="J407" s="5" t="n">
-        <v>0.015729</v>
-      </c>
-      <c r="K407" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.049878</v>
+      </c>
+      <c r="K407" s="5" t="n">
+        <v>0.122423</v>
       </c>
       <c r="L407" s="5" t="n">
-        <v>0.006589</v>
-      </c>
-      <c r="M407" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N407" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.134557</v>
+      </c>
+      <c r="M407" s="5" t="n">
+        <v>0.167231</v>
+      </c>
+      <c r="N407" s="5" t="n">
+        <v>0.171542</v>
       </c>
       <c r="O407" t="inlineStr">
         <is>
@@ -47171,7 +47165,7 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Net finance expense (income)</t>
+          <t>Chibougamau building expenses (note 16)</t>
         </is>
       </c>
       <c r="D408" t="inlineStr"/>
@@ -47205,21 +47199,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K408" s="5" t="n">
-        <v>-0.011748</v>
-      </c>
-      <c r="L408" s="5" t="n">
-        <v>0.005521</v>
-      </c>
-      <c r="M408" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N408" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L408" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M408" s="5" t="n">
+        <v>0.030412</v>
+      </c>
+      <c r="N408" s="5" t="n">
+        <v>0.033529</v>
       </c>
       <c r="O408" t="inlineStr">
         <is>
@@ -47260,19 +47254,15 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>and evaluation assets                                 −           129,463</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss $</t>
-        </is>
-      </c>
-      <c r="D409" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>and evaluation assets                                 −           129,463 total</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr"/>
       <c r="E409" t="inlineStr">
         <is>
           <t>-</t>
@@ -47303,21 +47293,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K409" s="5" t="n">
-        <v>-0.60141</v>
-      </c>
-      <c r="L409" s="5" t="n">
-        <v>-0.547556</v>
-      </c>
-      <c r="M409" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N409" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L409" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M409" s="5" t="n">
+        <v>1.177026</v>
+      </c>
+      <c r="N409" s="5" t="n">
+        <v>1.255279</v>
       </c>
       <c r="O409" t="inlineStr">
         <is>
@@ -47358,52 +47348,64 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>and evaluation assets                                 −           129,463</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Net loss per share, basic and diluted $</t>
+          <t>Interest income</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E410" s="5" t="n">
-        <v>-2e-08</v>
-      </c>
-      <c r="F410" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="G410" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="H410" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="I410" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="J410" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="K410" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="L410" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="M410" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N410" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J410" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L410" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M410" s="5" t="n">
+        <v>-2.7e-05</v>
+      </c>
+      <c r="N410" s="5" t="n">
+        <v>-0.000152</v>
       </c>
       <c r="O410" t="inlineStr">
         <is>
@@ -47444,17 +47446,17 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>and evaluation assets                                 −           129,463</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding</t>
+          <t>Interest expense</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>BasicAverageShares</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
@@ -47467,33 +47469,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G411" s="5" t="n">
-        <v>164.2518</v>
-      </c>
-      <c r="H411" s="5" t="n">
-        <v>174.383151</v>
-      </c>
-      <c r="I411" s="5" t="n">
-        <v>174.385206</v>
-      </c>
-      <c r="J411" s="5" t="n">
-        <v>188.591441</v>
-      </c>
-      <c r="K411" s="5" t="n">
-        <v>233.198404</v>
-      </c>
-      <c r="L411" s="5" t="n">
-        <v>263.400064</v>
-      </c>
-      <c r="M411" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N411" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M411" s="5" t="n">
+        <v>0.003156</v>
+      </c>
+      <c r="N411" s="5" t="n">
+        <v>0.027519</v>
       </c>
       <c r="O411" t="inlineStr">
         <is>
@@ -47534,15 +47544,19 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>and evaluation assets                                 −           129,463</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Administrative charges (note 19)</t>
-        </is>
-      </c>
-      <c r="D412" t="inlineStr"/>
+          <t>Net interest expense</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
       <c r="E412" t="inlineStr">
         <is>
           <t>-</t>
@@ -47563,29 +47577,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I412" s="5" t="n">
-        <v>0.941262</v>
-      </c>
-      <c r="J412" s="5" t="n">
-        <v>1.308328</v>
-      </c>
-      <c r="K412" s="5" t="n">
-        <v>0.78352</v>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L412" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M412" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N412" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M412" s="5" t="n">
+        <v>0.003129</v>
+      </c>
+      <c r="N412" s="5" t="n">
+        <v>0.027367</v>
       </c>
       <c r="O412" t="inlineStr">
         <is>
@@ -47626,12 +47642,12 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>and evaluation assets                                 −           129,463</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Chibougamau building expenses</t>
+          <t>Net (loss) income and comprehensive (loss) income $</t>
         </is>
       </c>
       <c r="D413" t="inlineStr"/>
@@ -47665,23 +47681,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K413" s="5" t="n">
-        <v>0.018576</v>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L413" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M413" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N413" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M413" s="5" t="n">
+        <v>1.720554</v>
+      </c>
+      <c r="N413" s="5" t="n">
+        <v>-1.004277</v>
       </c>
       <c r="O413" t="inlineStr">
         <is>
@@ -47722,15 +47736,19 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>and evaluation assets                                 −           129,463</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Net interest (income) expense</t>
-        </is>
-      </c>
-      <c r="D414" t="inlineStr"/>
+          <t>Net (loss) earnings per share, basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E414" t="inlineStr">
         <is>
           <t>-</t>
@@ -47756,26 +47774,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J414" s="5" t="n">
-        <v>0.009133</v>
-      </c>
-      <c r="K414" s="5" t="n">
-        <v>-0.011748</v>
+      <c r="J414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L414" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M414" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N414" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M414" s="5" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="N414" s="5" t="n">
+        <v>-1e-08</v>
       </c>
       <c r="O414" t="inlineStr">
         <is>
@@ -47816,17 +47834,17 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>and evaluation assets                                 −           129,463</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss $</t>
+          <t>Weighted average number of shares outstanding</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
@@ -47839,35 +47857,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G415" s="5" t="n">
-        <v>-1.138042</v>
-      </c>
-      <c r="H415" s="5" t="n">
-        <v>-1.014648</v>
-      </c>
-      <c r="I415" s="5" t="n">
-        <v>-1.204758</v>
-      </c>
-      <c r="J415" s="5" t="n">
-        <v>-1.519799</v>
-      </c>
-      <c r="K415" s="5" t="n">
-        <v>-0.60141</v>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L415" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M415" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N415" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M415" s="5" t="n">
+        <v>300.631488</v>
+      </c>
+      <c r="N415" s="5" t="n">
+        <v>308.111917</v>
       </c>
       <c r="O415" t="inlineStr">
         <is>
@@ -47908,17 +47932,17 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Revenues</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Net interest expense</t>
+          <t>Management fees $</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>InterestExpenseOperating</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
@@ -47942,20 +47966,16 @@
         </is>
       </c>
       <c r="I416" s="5" t="n">
-        <v>0.06635199999999999</v>
+        <v>0.030679</v>
       </c>
       <c r="J416" s="5" t="n">
-        <v>0.009133</v>
-      </c>
-      <c r="K416" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L416" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.087135</v>
+      </c>
+      <c r="K416" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="L416" s="5" t="n">
+        <v>0.040529</v>
       </c>
       <c r="M416" t="inlineStr">
         <is>
@@ -48011,7 +48031,7 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Other income related to flow-through shares</t>
+          <t>Other revenue related to flow-through shares</t>
         </is>
       </c>
       <c r="D417" t="inlineStr"/>
@@ -48030,8 +48050,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H417" s="5" t="n">
-        <v>0.256288</v>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I417" t="inlineStr">
         <is>
@@ -48043,15 +48065,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K417" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L417" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K417" s="5" t="n">
+        <v>0.358193</v>
+      </c>
+      <c r="L417" s="5" t="n">
+        <v>0.579881</v>
       </c>
       <c r="M417" t="inlineStr">
         <is>
@@ -48102,15 +48120,19 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Revenues</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Administrative charges (Note 15)</t>
-        </is>
-      </c>
-      <c r="D418" t="inlineStr"/>
+          <t>Revenues total</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
       <c r="E418" t="inlineStr">
         <is>
           <t>-</t>
@@ -48126,26 +48148,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H418" s="5" t="n">
-        <v>0.969727</v>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I418" s="5" t="n">
-        <v>0.941262</v>
-      </c>
-      <c r="J418" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K418" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L418" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.07267899999999999</v>
+      </c>
+      <c r="J418" s="5" t="n">
+        <v>0.119135</v>
+      </c>
+      <c r="K418" s="5" t="n">
+        <v>0.414783</v>
+      </c>
+      <c r="L418" s="5" t="n">
+        <v>0.672945</v>
       </c>
       <c r="M418" t="inlineStr">
         <is>
@@ -48201,7 +48219,7 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Net interest expense (income)</t>
+          <t>Administrative charges (note 16)</t>
         </is>
       </c>
       <c r="D419" t="inlineStr"/>
@@ -48220,26 +48238,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H419" s="5" t="n">
-        <v>-0.003515</v>
-      </c>
-      <c r="I419" s="5" t="n">
-        <v>0.06635199999999999</v>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J419" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K419" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L419" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K419" s="5" t="n">
+        <v>0.773477</v>
+      </c>
+      <c r="L419" s="5" t="n">
+        <v>0.978755</v>
       </c>
       <c r="M419" t="inlineStr">
         <is>
@@ -48290,19 +48308,15 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Operating</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss $</t>
-        </is>
-      </c>
-      <c r="D420" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Chibougamau building expenses (note 17)</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr"/>
       <c r="E420" t="inlineStr">
         <is>
           <t>-</t>
@@ -48313,29 +48327,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G420" s="5" t="n">
-        <v>-1.138042</v>
-      </c>
-      <c r="H420" s="5" t="n">
-        <v>-1.014648</v>
-      </c>
-      <c r="I420" s="5" t="n">
-        <v>-1.204758</v>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J420" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K420" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L420" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K420" s="5" t="n">
+        <v>0.028619</v>
+      </c>
+      <c r="L420" s="5" t="n">
+        <v>0.061895</v>
       </c>
       <c r="M420" t="inlineStr">
         <is>
@@ -48386,50 +48402,42 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Share-based payments</t>
-        </is>
-      </c>
-      <c r="D421" t="inlineStr"/>
-      <c r="E421" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F421" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G421" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Expenses total</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E421" s="5" t="n">
+        <v>2.108847</v>
+      </c>
+      <c r="F421" s="5" t="n">
+        <v>1.651232</v>
+      </c>
+      <c r="G421" s="5" t="n">
+        <v>1.144212</v>
       </c>
       <c r="H421" s="5" t="n">
-        <v>0.299926</v>
+        <v>1.274451</v>
       </c>
       <c r="I421" s="5" t="n">
-        <v>0.265975</v>
-      </c>
-      <c r="J421" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K421" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L421" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.211085</v>
+      </c>
+      <c r="J421" s="5" t="n">
+        <v>1.629801</v>
+      </c>
+      <c r="K421" s="5" t="n">
+        <v>1.027941</v>
+      </c>
+      <c r="L421" s="5" t="n">
+        <v>1.21498</v>
       </c>
       <c r="M421" t="inlineStr">
         <is>
@@ -48480,15 +48488,19 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Other revenue related to flow-through shares</t>
-        </is>
-      </c>
-      <c r="D422" t="inlineStr"/>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
       <c r="E422" t="inlineStr">
         <is>
           <t>-</t>
@@ -48499,33 +48511,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G422" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G422" s="5" t="n">
+        <v>0.00617</v>
       </c>
       <c r="H422" s="5" t="n">
-        <v>-0.256288</v>
-      </c>
-      <c r="I422" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J422" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K422" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L422" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.003515</v>
+      </c>
+      <c r="I422" s="5" t="n">
+        <v>-1e-05</v>
+      </c>
+      <c r="J422" s="5" t="n">
+        <v>-0.006596</v>
+      </c>
+      <c r="K422" s="5" t="n">
+        <v>-0.011748</v>
+      </c>
+      <c r="L422" s="5" t="n">
+        <v>-0.001068</v>
       </c>
       <c r="M422" t="inlineStr">
         <is>
@@ -48576,12 +48578,12 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Net interest expense</t>
+          <t>Interest expense</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
@@ -48604,26 +48606,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H423" s="5" t="n">
-        <v>-0.003515</v>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I423" s="5" t="n">
-        <v>0.06635199999999999</v>
-      </c>
-      <c r="J423" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.066362</v>
+      </c>
+      <c r="J423" s="5" t="n">
+        <v>0.015729</v>
       </c>
       <c r="K423" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L423" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L423" s="5" t="n">
+        <v>0.006589</v>
       </c>
       <c r="M423" t="inlineStr">
         <is>
@@ -48674,12 +48674,12 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Net change in non-cash operating working capital items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Change in tax credits and other receivables</t>
+          <t>Net finance expense (income)</t>
         </is>
       </c>
       <c r="D424" t="inlineStr"/>
@@ -48698,26 +48698,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H424" s="5" t="n">
-        <v>-0.023377</v>
-      </c>
-      <c r="I424" s="5" t="n">
-        <v>0.092268</v>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J424" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K424" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L424" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K424" s="5" t="n">
+        <v>-0.011748</v>
+      </c>
+      <c r="L424" s="5" t="n">
+        <v>0.005521</v>
       </c>
       <c r="M424" t="inlineStr">
         <is>
@@ -48768,15 +48768,19 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Net change in non-cash operating working capital items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Change in prepaid expenses</t>
-        </is>
-      </c>
-      <c r="D425" t="inlineStr"/>
+          <t>Net loss and comprehensive loss $</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E425" t="inlineStr">
         <is>
           <t>-</t>
@@ -48792,26 +48796,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H425" s="5" t="n">
-        <v>0.012685</v>
-      </c>
-      <c r="I425" s="5" t="n">
-        <v>0.010495</v>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J425" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K425" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L425" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K425" s="5" t="n">
+        <v>-0.60141</v>
+      </c>
+      <c r="L425" s="5" t="n">
+        <v>-0.547556</v>
       </c>
       <c r="M425" t="inlineStr">
         <is>
@@ -48862,50 +48866,42 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Net change in non-cash operating working capital items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Change in accounts payable and accrued liabilities</t>
-        </is>
-      </c>
-      <c r="D426" t="inlineStr"/>
-      <c r="E426" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F426" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G426" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net loss per share, basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E426" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="F426" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="G426" s="5" t="n">
+        <v>-1e-08</v>
       </c>
       <c r="H426" s="5" t="n">
-        <v>0.076892</v>
+        <v>-1e-08</v>
       </c>
       <c r="I426" s="5" t="n">
-        <v>-0.023865</v>
-      </c>
-      <c r="J426" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K426" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L426" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1e-08</v>
+      </c>
+      <c r="J426" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="K426" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="L426" s="5" t="n">
+        <v>-1e-08</v>
       </c>
       <c r="M426" t="inlineStr">
         <is>
@@ -48956,15 +48952,19 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Net change in non-cash operating working capital items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Change in Gold Fields prepayment</t>
-        </is>
-      </c>
-      <c r="D427" t="inlineStr"/>
+          <t>Weighted average number of shares outstanding</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
       <c r="E427" t="inlineStr">
         <is>
           <t>-</t>
@@ -48975,33 +48975,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G427" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H427" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G427" s="5" t="n">
+        <v>164.2518</v>
+      </c>
+      <c r="H427" s="5" t="n">
+        <v>174.383151</v>
       </c>
       <c r="I427" s="5" t="n">
-        <v>0.112</v>
-      </c>
-      <c r="J427" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K427" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L427" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>174.385206</v>
+      </c>
+      <c r="J427" s="5" t="n">
+        <v>188.591441</v>
+      </c>
+      <c r="K427" s="5" t="n">
+        <v>233.198404</v>
+      </c>
+      <c r="L427" s="5" t="n">
+        <v>263.400064</v>
       </c>
       <c r="M427" t="inlineStr">
         <is>
@@ -49052,12 +49042,12 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Net change in non-cash operating working capital items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Interest received</t>
+          <t>Administrative charges (note 19)</t>
         </is>
       </c>
       <c r="D428" t="inlineStr"/>
@@ -49076,21 +49066,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H428" s="5" t="n">
-        <v>0.003515</v>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I428" s="5" t="n">
-        <v>1e-05</v>
-      </c>
-      <c r="J428" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K428" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.941262</v>
+      </c>
+      <c r="J428" s="5" t="n">
+        <v>1.308328</v>
+      </c>
+      <c r="K428" s="5" t="n">
+        <v>0.78352</v>
       </c>
       <c r="L428" t="inlineStr">
         <is>
@@ -49146,12 +49134,12 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Net change in non-cash operating working capital items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Interest paid</t>
+          <t>Chibougamau building expenses</t>
         </is>
       </c>
       <c r="D429" t="inlineStr"/>
@@ -49175,18 +49163,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I429" s="5" t="n">
-        <v>-0.004352</v>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J429" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K429" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K429" s="5" t="n">
+        <v>0.018576</v>
       </c>
       <c r="L429" t="inlineStr">
         <is>
@@ -49242,12 +49230,12 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Net change in non-cash operating working capital items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Net cash used in operating activities</t>
+          <t>Net interest (income) expense</t>
         </is>
       </c>
       <c r="D430" t="inlineStr"/>
@@ -49266,21 +49254,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H430" s="5" t="n">
-        <v>-0.90481</v>
-      </c>
-      <c r="I430" s="5" t="n">
-        <v>-0.685875</v>
-      </c>
-      <c r="J430" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K430" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J430" s="5" t="n">
+        <v>0.009133</v>
+      </c>
+      <c r="K430" s="5" t="n">
+        <v>-0.011748</v>
       </c>
       <c r="L430" t="inlineStr">
         <is>
@@ -49336,15 +49324,19 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Additions to mining properties and exploration</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Additions to mining properties and exploration and evaluation assets</t>
-        </is>
-      </c>
-      <c r="D431" t="inlineStr"/>
+          <t>Loss and comprehensive loss $</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E431" t="inlineStr">
         <is>
           <t>-</t>
@@ -49356,23 +49348,19 @@
         </is>
       </c>
       <c r="G431" s="5" t="n">
-        <v>-2.375011</v>
+        <v>-1.138042</v>
       </c>
       <c r="H431" s="5" t="n">
-        <v>-1.999619</v>
+        <v>-1.014648</v>
       </c>
       <c r="I431" s="5" t="n">
-        <v>-0.315961</v>
-      </c>
-      <c r="J431" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K431" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.204758</v>
+      </c>
+      <c r="J431" s="5" t="n">
+        <v>-1.519799</v>
+      </c>
+      <c r="K431" s="5" t="n">
+        <v>-0.60141</v>
       </c>
       <c r="L431" t="inlineStr">
         <is>
@@ -49428,15 +49416,19 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Additions to mining properties and exploration</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Credit on mining duties and resource tax credits</t>
-        </is>
-      </c>
-      <c r="D432" t="inlineStr"/>
+          <t>Net interest expense</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
       <c r="E432" t="inlineStr">
         <is>
           <t>-</t>
@@ -49447,19 +49439,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G432" s="5" t="n">
-        <v>0.568078</v>
-      </c>
-      <c r="H432" s="5" t="n">
-        <v>1.062422</v>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I432" s="5" t="n">
-        <v>0.050021</v>
-      </c>
-      <c r="J432" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.06635199999999999</v>
+      </c>
+      <c r="J432" s="5" t="n">
+        <v>0.009133</v>
       </c>
       <c r="K432" t="inlineStr">
         <is>
@@ -49520,12 +49514,12 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Additions to mining properties and exploration</t>
+          <t>Revenues</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Net cash used in investing activities</t>
+          <t>Other income related to flow-through shares</t>
         </is>
       </c>
       <c r="D433" t="inlineStr"/>
@@ -49545,10 +49539,12 @@
         </is>
       </c>
       <c r="H433" s="5" t="n">
-        <v>-0.9371969999999999</v>
-      </c>
-      <c r="I433" s="5" t="n">
-        <v>-0.26594</v>
+        <v>0.256288</v>
+      </c>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J433" t="inlineStr">
         <is>
@@ -49614,12 +49610,12 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Financing</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Proceeds from issuance of shares</t>
+          <t>Administrative charges (Note 15)</t>
         </is>
       </c>
       <c r="D434" t="inlineStr"/>
@@ -49633,16 +49629,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G434" s="5" t="n">
-        <v>2.440626</v>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H434" s="5" t="n">
-        <v>0.002667</v>
-      </c>
-      <c r="I434" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.969727</v>
+      </c>
+      <c r="I434" s="5" t="n">
+        <v>0.941262</v>
       </c>
       <c r="J434" t="inlineStr">
         <is>
@@ -49708,12 +49704,12 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Financing</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Equity financing expenses</t>
+          <t>Net interest expense (income)</t>
         </is>
       </c>
       <c r="D435" t="inlineStr"/>
@@ -49733,10 +49729,10 @@
         </is>
       </c>
       <c r="H435" s="5" t="n">
-        <v>-0.006903</v>
+        <v>-0.003515</v>
       </c>
       <c r="I435" s="5" t="n">
-        <v>-0.03216</v>
+        <v>0.06635199999999999</v>
       </c>
       <c r="J435" t="inlineStr">
         <is>
@@ -49802,15 +49798,19 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Financing</t>
+          <t>Operating</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Increase in due to directors and shareholders</t>
-        </is>
-      </c>
-      <c r="D436" t="inlineStr"/>
+          <t>Loss and comprehensive loss $</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E436" t="inlineStr">
         <is>
           <t>-</t>
@@ -49821,18 +49821,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G436" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H436" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G436" s="5" t="n">
+        <v>-1.138042</v>
+      </c>
+      <c r="H436" s="5" t="n">
+        <v>-1.014648</v>
       </c>
       <c r="I436" s="5" t="n">
-        <v>0.606</v>
+        <v>-1.204758</v>
       </c>
       <c r="J436" t="inlineStr">
         <is>
@@ -49898,12 +49894,12 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Financing</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Decrease in due to directors and shareholders</t>
+          <t>Share-based payments</t>
         </is>
       </c>
       <c r="D437" t="inlineStr"/>
@@ -49922,13 +49918,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H437" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H437" s="5" t="n">
+        <v>0.299926</v>
       </c>
       <c r="I437" s="5" t="n">
-        <v>-0.125</v>
+        <v>0.265975</v>
       </c>
       <c r="J437" t="inlineStr">
         <is>
@@ -49994,12 +49988,12 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Financing</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Short-term loan</t>
+          <t>Other revenue related to flow-through shares</t>
         </is>
       </c>
       <c r="D438" t="inlineStr"/>
@@ -50018,13 +50012,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H438" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I438" s="5" t="n">
-        <v>0.5</v>
+      <c r="H438" s="5" t="n">
+        <v>-0.256288</v>
+      </c>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J438" t="inlineStr">
         <is>
@@ -50090,15 +50084,19 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Financing</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Net cash from (used in) financing activities</t>
-        </is>
-      </c>
-      <c r="D439" t="inlineStr"/>
+          <t>Net interest expense</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
       <c r="E439" t="inlineStr">
         <is>
           <t>-</t>
@@ -50115,10 +50113,10 @@
         </is>
       </c>
       <c r="H439" s="5" t="n">
-        <v>-0.004236</v>
+        <v>-0.003515</v>
       </c>
       <c r="I439" s="5" t="n">
-        <v>0.94884</v>
+        <v>0.06635199999999999</v>
       </c>
       <c r="J439" t="inlineStr">
         <is>
@@ -50184,12 +50182,12 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Financing</t>
+          <t>Net change in non-cash operating working capital items</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Net decrease in cash and cash equivalents</t>
+          <t>Change in tax credits and other receivables</t>
         </is>
       </c>
       <c r="D440" t="inlineStr"/>
@@ -50203,14 +50201,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G440" s="5" t="n">
-        <v>-0.6960809999999999</v>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H440" s="5" t="n">
-        <v>-1.846243</v>
+        <v>-0.023377</v>
       </c>
       <c r="I440" s="5" t="n">
-        <v>-0.002975</v>
+        <v>0.092268</v>
       </c>
       <c r="J440" t="inlineStr">
         <is>
@@ -50276,12 +50276,12 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Financing</t>
+          <t>Net change in non-cash operating working capital items</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, beginning of year</t>
+          <t>Change in prepaid expenses</t>
         </is>
       </c>
       <c r="D441" t="inlineStr"/>
@@ -50295,14 +50295,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G441" s="5" t="n">
-        <v>2.602862</v>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H441" s="5" t="n">
-        <v>1.906781</v>
+        <v>0.012685</v>
       </c>
       <c r="I441" s="5" t="n">
-        <v>0.060538</v>
+        <v>0.010495</v>
       </c>
       <c r="J441" t="inlineStr">
         <is>
@@ -50368,12 +50370,12 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Financing</t>
+          <t>Net change in non-cash operating working capital items</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, end of year $</t>
+          <t>Change in accounts payable and accrued liabilities</t>
         </is>
       </c>
       <c r="D442" t="inlineStr"/>
@@ -50387,14 +50389,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G442" s="5" t="n">
-        <v>1.906781</v>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H442" s="5" t="n">
-        <v>0.060538</v>
+        <v>0.076892</v>
       </c>
       <c r="I442" s="5" t="n">
-        <v>0.057563</v>
+        <v>-0.023865</v>
       </c>
       <c r="J442" t="inlineStr">
         <is>
@@ -50460,12 +50464,12 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Net change in non-cash operating working capital items</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Administrative charges $</t>
+          <t>Change in Gold Fields prepayment</t>
         </is>
       </c>
       <c r="D443" t="inlineStr"/>
@@ -50479,16 +50483,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G443" s="5" t="n">
-        <v>0.996556</v>
-      </c>
-      <c r="H443" s="5" t="n">
-        <v>0.969727</v>
-      </c>
-      <c r="I443" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I443" s="5" t="n">
+        <v>0.112</v>
       </c>
       <c r="J443" t="inlineStr">
         <is>
@@ -50554,12 +50560,12 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Net change in non-cash operating working capital items</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Other revenue related to flow-through shares</t>
+          <t>Interest received</t>
         </is>
       </c>
       <c r="D444" t="inlineStr"/>
@@ -50579,12 +50585,10 @@
         </is>
       </c>
       <c r="H444" s="5" t="n">
-        <v>0.256288</v>
-      </c>
-      <c r="I444" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.003515</v>
+      </c>
+      <c r="I444" s="5" t="n">
+        <v>1e-05</v>
       </c>
       <c r="J444" t="inlineStr">
         <is>
@@ -50650,12 +50654,12 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Adjustments for</t>
+          <t>Net change in non-cash operating working capital items</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Share-based payments</t>
+          <t>Interest paid</t>
         </is>
       </c>
       <c r="D445" t="inlineStr"/>
@@ -50669,16 +50673,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G445" s="5" t="n">
-        <v>0.139573</v>
-      </c>
-      <c r="H445" s="5" t="n">
-        <v>0.299926</v>
-      </c>
-      <c r="I445" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I445" s="5" t="n">
+        <v>-0.004352</v>
       </c>
       <c r="J445" t="inlineStr">
         <is>
@@ -50744,12 +50750,12 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Adjustments for</t>
+          <t>Net change in non-cash operating working capital items</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Other revenue related to flow-through shares</t>
+          <t>Net cash used in operating activities</t>
         </is>
       </c>
       <c r="D446" t="inlineStr"/>
@@ -50769,12 +50775,10 @@
         </is>
       </c>
       <c r="H446" s="5" t="n">
-        <v>-0.256288</v>
-      </c>
-      <c r="I446" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.90481</v>
+      </c>
+      <c r="I446" s="5" t="n">
+        <v>-0.685875</v>
       </c>
       <c r="J446" t="inlineStr">
         <is>
@@ -50840,19 +50844,15 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Adjustments for</t>
+          <t>Additions to mining properties and exploration</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D447" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>Additions to mining properties and exploration and evaluation assets</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr"/>
       <c r="E447" t="inlineStr">
         <is>
           <t>-</t>
@@ -50864,15 +50864,13 @@
         </is>
       </c>
       <c r="G447" s="5" t="n">
-        <v>-0.00617</v>
+        <v>-2.375011</v>
       </c>
       <c r="H447" s="5" t="n">
-        <v>-0.003515</v>
-      </c>
-      <c r="I447" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.999619</v>
+      </c>
+      <c r="I447" s="5" t="n">
+        <v>-0.315961</v>
       </c>
       <c r="J447" t="inlineStr">
         <is>
@@ -50938,12 +50936,12 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Working capital adjustments</t>
+          <t>Additions to mining properties and exploration</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Change in current tax and other receivables</t>
+          <t>Credit on mining duties and resource tax credits</t>
         </is>
       </c>
       <c r="D448" t="inlineStr"/>
@@ -50958,15 +50956,13 @@
         </is>
       </c>
       <c r="G448" s="5" t="n">
-        <v>-0.046772</v>
+        <v>0.568078</v>
       </c>
       <c r="H448" s="5" t="n">
-        <v>-0.023377</v>
-      </c>
-      <c r="I448" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.062422</v>
+      </c>
+      <c r="I448" s="5" t="n">
+        <v>0.050021</v>
       </c>
       <c r="J448" t="inlineStr">
         <is>
@@ -51032,12 +51028,12 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Working capital adjustments</t>
+          <t>Additions to mining properties and exploration</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Change in prepaid expenses</t>
+          <t>Net cash used in investing activities</t>
         </is>
       </c>
       <c r="D449" t="inlineStr"/>
@@ -51051,16 +51047,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G449" s="5" t="n">
-        <v>-0.007443</v>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H449" s="5" t="n">
-        <v>0.012685</v>
-      </c>
-      <c r="I449" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.9371969999999999</v>
+      </c>
+      <c r="I449" s="5" t="n">
+        <v>-0.26594</v>
       </c>
       <c r="J449" t="inlineStr">
         <is>
@@ -51126,12 +51122,12 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Working capital adjustments</t>
+          <t>Financing</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Change in accounts payable and accrued liabilities</t>
+          <t>Proceeds from issuance of shares</t>
         </is>
       </c>
       <c r="D450" t="inlineStr"/>
@@ -51146,10 +51142,10 @@
         </is>
       </c>
       <c r="G450" s="5" t="n">
-        <v>0.035381</v>
+        <v>2.440626</v>
       </c>
       <c r="H450" s="5" t="n">
-        <v>0.076892</v>
+        <v>0.002667</v>
       </c>
       <c r="I450" t="inlineStr">
         <is>
@@ -51220,12 +51216,12 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Working capital adjustments</t>
+          <t>Financing</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Interest received</t>
+          <t>Equity financing expenses</t>
         </is>
       </c>
       <c r="D451" t="inlineStr"/>
@@ -51239,16 +51235,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G451" s="5" t="n">
-        <v>0.00617</v>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H451" s="5" t="n">
-        <v>0.003515</v>
-      </c>
-      <c r="I451" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.006903</v>
+      </c>
+      <c r="I451" s="5" t="n">
+        <v>-0.03216</v>
       </c>
       <c r="J451" t="inlineStr">
         <is>
@@ -51314,12 +51310,12 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Working capital adjustments</t>
+          <t>Financing</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Working capital adjustments total</t>
+          <t>Increase in due to directors and shareholders</t>
         </is>
       </c>
       <c r="D452" t="inlineStr"/>
@@ -51333,16 +51329,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G452" s="5" t="n">
-        <v>-1.017303</v>
-      </c>
-      <c r="H452" s="5" t="n">
-        <v>-0.90481</v>
-      </c>
-      <c r="I452" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I452" s="5" t="n">
+        <v>0.606</v>
       </c>
       <c r="J452" t="inlineStr">
         <is>
@@ -51408,12 +51406,12 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Additions to mining properties and exploration</t>
+          <t>Financing</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Additions to mining properties and exploration total</t>
+          <t>Decrease in due to directors and shareholders</t>
         </is>
       </c>
       <c r="D453" t="inlineStr"/>
@@ -51427,16 +51425,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G453" s="5" t="n">
-        <v>-1.806933</v>
-      </c>
-      <c r="H453" s="5" t="n">
-        <v>-0.9371969999999999</v>
-      </c>
-      <c r="I453" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I453" s="5" t="n">
+        <v>-0.125</v>
       </c>
       <c r="J453" t="inlineStr">
         <is>
@@ -51507,7 +51507,7 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Share issue expenses</t>
+          <t>Short-term loan</t>
         </is>
       </c>
       <c r="D454" t="inlineStr"/>
@@ -51521,16 +51521,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G454" s="5" t="n">
-        <v>-0.312471</v>
-      </c>
-      <c r="H454" s="5" t="n">
-        <v>-0.006903</v>
-      </c>
-      <c r="I454" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I454" s="5" t="n">
+        <v>0.5</v>
       </c>
       <c r="J454" t="inlineStr">
         <is>
@@ -51601,7 +51603,7 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Financing total</t>
+          <t>Net cash from (used in) financing activities</t>
         </is>
       </c>
       <c r="D455" t="inlineStr"/>
@@ -51615,16 +51617,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G455" s="5" t="n">
-        <v>2.128155</v>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H455" s="5" t="n">
         <v>-0.004236</v>
       </c>
-      <c r="I455" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I455" s="5" t="n">
+        <v>0.94884</v>
       </c>
       <c r="J455" t="inlineStr">
         <is>
@@ -51690,12 +51692,12 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Non-cash financing activity</t>
+          <t>Financing</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Warrants with respect to share issuance expenses $</t>
+          <t>Net decrease in cash and cash equivalents</t>
         </is>
       </c>
       <c r="D456" t="inlineStr"/>
@@ -51710,17 +51712,13 @@
         </is>
       </c>
       <c r="G456" s="5" t="n">
-        <v>0.013023</v>
-      </c>
-      <c r="H456" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I456" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.6960809999999999</v>
+      </c>
+      <c r="H456" s="5" t="n">
+        <v>-1.846243</v>
+      </c>
+      <c r="I456" s="5" t="n">
+        <v>-0.002975</v>
       </c>
       <c r="J456" t="inlineStr">
         <is>
@@ -51784,33 +51782,35 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B457" t="inlineStr"/>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>Financing</t>
+        </is>
+      </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Interest revenue and other $</t>
+          <t>Cash and cash equivalents, beginning of year</t>
         </is>
       </c>
       <c r="D457" t="inlineStr"/>
-      <c r="E457" s="5" t="n">
-        <v>0.03082</v>
-      </c>
-      <c r="F457" s="5" t="n">
-        <v>0.001188</v>
-      </c>
-      <c r="G457" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H457" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I457" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G457" s="5" t="n">
+        <v>2.602862</v>
+      </c>
+      <c r="H457" s="5" t="n">
+        <v>1.906781</v>
+      </c>
+      <c r="I457" s="5" t="n">
+        <v>0.060538</v>
       </c>
       <c r="J457" t="inlineStr">
         <is>
@@ -51876,35 +51876,33 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Administrative charges</t>
+          <t>Cash and cash equivalents, end of year $</t>
         </is>
       </c>
       <c r="D458" t="inlineStr"/>
-      <c r="E458" s="5" t="n">
-        <v>0.998578</v>
-      </c>
-      <c r="F458" s="5" t="n">
-        <v>1.240299</v>
-      </c>
-      <c r="G458" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H458" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I458" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G458" s="5" t="n">
+        <v>1.906781</v>
+      </c>
+      <c r="H458" s="5" t="n">
+        <v>0.060538</v>
+      </c>
+      <c r="I458" s="5" t="n">
+        <v>0.057563</v>
       </c>
       <c r="J458" t="inlineStr">
         <is>
@@ -51975,25 +51973,25 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Stock-based compensation (note 7)</t>
+          <t>Administrative charges $</t>
         </is>
       </c>
       <c r="D459" t="inlineStr"/>
-      <c r="E459" s="5" t="n">
-        <v>0.242417</v>
-      </c>
-      <c r="F459" s="5" t="n">
-        <v>0.300834</v>
-      </c>
-      <c r="G459" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H459" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G459" s="5" t="n">
+        <v>0.996556</v>
+      </c>
+      <c r="H459" s="5" t="n">
+        <v>0.969727</v>
       </c>
       <c r="I459" t="inlineStr">
         <is>
@@ -52069,25 +52067,27 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>Tax on capital</t>
+          <t>Other revenue related to flow-through shares</t>
         </is>
       </c>
       <c r="D460" t="inlineStr"/>
-      <c r="E460" s="5" t="n">
-        <v>0.08400000000000001</v>
-      </c>
-      <c r="F460" s="5" t="n">
-        <v>0.08400000000000001</v>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G460" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H460" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H460" s="5" t="n">
+        <v>0.256288</v>
       </c>
       <c r="I460" t="inlineStr">
         <is>
@@ -52158,30 +52158,30 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Financial expenses</t>
+          <t>Share-based payments</t>
         </is>
       </c>
       <c r="D461" t="inlineStr"/>
-      <c r="E461" s="5" t="n">
-        <v>0.004091</v>
-      </c>
-      <c r="F461" s="5" t="n">
-        <v>0.004877</v>
-      </c>
-      <c r="G461" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H461" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G461" s="5" t="n">
+        <v>0.139573</v>
+      </c>
+      <c r="H461" s="5" t="n">
+        <v>0.299926</v>
       </c>
       <c r="I461" t="inlineStr">
         <is>
@@ -52252,17 +52252,19 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Loss on write-down of exploration assets</t>
+          <t>Other revenue related to flow-through shares</t>
         </is>
       </c>
       <c r="D462" t="inlineStr"/>
-      <c r="E462" s="5" t="n">
-        <v>0.768425</v>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -52274,10 +52276,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H462" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H462" s="5" t="n">
+        <v>-0.256288</v>
       </c>
       <c r="I462" t="inlineStr">
         <is>
@@ -52348,34 +52348,34 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Loss before income taxes</t>
+          <t>Interest income</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
-      <c r="E463" s="5" t="n">
-        <v>-2.078027</v>
-      </c>
-      <c r="F463" s="5" t="n">
-        <v>-1.650044</v>
-      </c>
-      <c r="G463" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H463" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G463" s="5" t="n">
+        <v>-0.00617</v>
+      </c>
+      <c r="H463" s="5" t="n">
+        <v>-0.003515</v>
       </c>
       <c r="I463" t="inlineStr">
         <is>
@@ -52446,36 +52446,30 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Working capital adjustments</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Future income taxes (note 10)</t>
-        </is>
-      </c>
-      <c r="D464" t="inlineStr">
-        <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
+          <t>Change in current tax and other receivables</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr"/>
       <c r="E464" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F464" s="5" t="n">
-        <v>0.296</v>
-      </c>
-      <c r="G464" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H464" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G464" s="5" t="n">
+        <v>-0.046772</v>
+      </c>
+      <c r="H464" s="5" t="n">
+        <v>-0.023377</v>
       </c>
       <c r="I464" t="inlineStr">
         <is>
@@ -52546,34 +52540,30 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Working capital adjustments</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss</t>
-        </is>
-      </c>
-      <c r="D465" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E465" s="5" t="n">
-        <v>-2.078027</v>
-      </c>
-      <c r="F465" s="5" t="n">
-        <v>-1.354044</v>
-      </c>
-      <c r="G465" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H465" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Change in prepaid expenses</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr"/>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G465" s="5" t="n">
+        <v>-0.007443</v>
+      </c>
+      <c r="H465" s="5" t="n">
+        <v>0.012685</v>
       </c>
       <c r="I465" t="inlineStr">
         <is>
@@ -52644,30 +52634,30 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Working capital adjustments</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Deficit, beginning of year</t>
+          <t>Change in accounts payable and accrued liabilities</t>
         </is>
       </c>
       <c r="D466" t="inlineStr"/>
-      <c r="E466" s="5" t="n">
-        <v>-18.141702</v>
-      </c>
-      <c r="F466" s="5" t="n">
-        <v>-20.394572</v>
-      </c>
-      <c r="G466" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H466" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G466" s="5" t="n">
+        <v>0.035381</v>
+      </c>
+      <c r="H466" s="5" t="n">
+        <v>0.076892</v>
       </c>
       <c r="I466" t="inlineStr">
         <is>
@@ -52738,30 +52728,30 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Working capital adjustments</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>Share issue expense</t>
+          <t>Interest received</t>
         </is>
       </c>
       <c r="D467" t="inlineStr"/>
-      <c r="E467" s="5" t="n">
-        <v>-0.174843</v>
-      </c>
-      <c r="F467" s="5" t="n">
-        <v>-0.5026969999999999</v>
-      </c>
-      <c r="G467" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H467" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G467" s="5" t="n">
+        <v>0.00617</v>
+      </c>
+      <c r="H467" s="5" t="n">
+        <v>0.003515</v>
       </c>
       <c r="I467" t="inlineStr">
         <is>
@@ -52832,12 +52822,12 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Working capital adjustments</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Future income taxes arising from flow-through shares</t>
+          <t>Working capital adjustments total</t>
         </is>
       </c>
       <c r="D468" t="inlineStr"/>
@@ -52846,18 +52836,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F468" s="5" t="n">
-        <v>-0.296</v>
-      </c>
-      <c r="G468" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H468" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G468" s="5" t="n">
+        <v>-1.017303</v>
+      </c>
+      <c r="H468" s="5" t="n">
+        <v>-0.90481</v>
       </c>
       <c r="I468" t="inlineStr">
         <is>
@@ -52928,87 +52916,1607 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
+          <t>Additions to mining properties and exploration</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>Additions to mining properties and exploration total</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr"/>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G469" s="5" t="n">
+        <v>-1.806933</v>
+      </c>
+      <c r="H469" s="5" t="n">
+        <v>-0.9371969999999999</v>
+      </c>
+      <c r="I469" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J469" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L469" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M469" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N469" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O469" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P469" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q469" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R469" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S469" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T469" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>Financing</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>Share issue expenses</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr"/>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G470" s="5" t="n">
+        <v>-0.312471</v>
+      </c>
+      <c r="H470" s="5" t="n">
+        <v>-0.006903</v>
+      </c>
+      <c r="I470" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J470" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L470" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M470" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N470" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O470" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P470" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q470" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R470" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S470" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T470" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>Financing</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>Financing total</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr"/>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G471" s="5" t="n">
+        <v>2.128155</v>
+      </c>
+      <c r="H471" s="5" t="n">
+        <v>-0.004236</v>
+      </c>
+      <c r="I471" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J471" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L471" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M471" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N471" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O471" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P471" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q471" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R471" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S471" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T471" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>Non-cash financing activity</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>Warrants with respect to share issuance expenses $</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr"/>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G472" s="5" t="n">
+        <v>0.013023</v>
+      </c>
+      <c r="H472" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I472" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J472" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L472" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M472" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N472" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O472" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P472" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q472" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R472" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S472" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T472" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr"/>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>Interest revenue and other $</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr"/>
+      <c r="E473" s="5" t="n">
+        <v>0.03082</v>
+      </c>
+      <c r="F473" s="5" t="n">
+        <v>0.001188</v>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H473" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I473" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J473" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L473" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M473" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N473" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O473" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P473" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q473" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R473" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S473" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T473" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
           <t>Expenses</t>
         </is>
       </c>
-      <c r="C469" t="inlineStr">
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>Administrative charges</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr"/>
+      <c r="E474" s="5" t="n">
+        <v>0.998578</v>
+      </c>
+      <c r="F474" s="5" t="n">
+        <v>1.240299</v>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H474" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I474" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J474" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L474" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M474" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N474" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O474" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P474" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q474" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R474" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S474" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T474" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>Stock-based compensation (note 7)</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr"/>
+      <c r="E475" s="5" t="n">
+        <v>0.242417</v>
+      </c>
+      <c r="F475" s="5" t="n">
+        <v>0.300834</v>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H475" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I475" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J475" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L475" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M475" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N475" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O475" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P475" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q475" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R475" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S475" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T475" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>Tax on capital</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr"/>
+      <c r="E476" s="5" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="F476" s="5" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H476" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I476" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J476" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L476" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M476" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N476" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O476" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P476" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q476" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R476" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S476" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T476" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>Financial expenses</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr"/>
+      <c r="E477" s="5" t="n">
+        <v>0.004091</v>
+      </c>
+      <c r="F477" s="5" t="n">
+        <v>0.004877</v>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H477" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I477" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J477" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L477" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M477" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N477" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O477" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P477" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q477" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R477" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S477" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T477" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>Loss on write-down of exploration assets</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr"/>
+      <c r="E478" s="5" t="n">
+        <v>0.768425</v>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H478" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I478" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J478" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L478" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M478" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N478" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O478" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P478" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q478" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R478" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S478" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T478" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>Loss before income taxes</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
+      <c r="E479" s="5" t="n">
+        <v>-2.078027</v>
+      </c>
+      <c r="F479" s="5" t="n">
+        <v>-1.650044</v>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H479" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I479" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J479" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L479" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M479" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N479" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O479" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P479" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q479" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R479" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S479" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T479" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>Future income taxes (note 10)</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F480" s="5" t="n">
+        <v>0.296</v>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H480" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I480" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J480" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L480" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M480" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N480" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O480" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P480" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q480" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R480" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S480" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T480" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E481" s="5" t="n">
+        <v>-2.078027</v>
+      </c>
+      <c r="F481" s="5" t="n">
+        <v>-1.354044</v>
+      </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H481" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I481" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J481" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L481" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M481" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N481" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O481" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P481" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q481" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R481" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S481" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T481" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>Deficit, beginning of year</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr"/>
+      <c r="E482" s="5" t="n">
+        <v>-18.141702</v>
+      </c>
+      <c r="F482" s="5" t="n">
+        <v>-20.394572</v>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>Share issue expense</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr"/>
+      <c r="E483" s="5" t="n">
+        <v>-0.174843</v>
+      </c>
+      <c r="F483" s="5" t="n">
+        <v>-0.5026969999999999</v>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>Future income taxes arising from flow-through shares</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr"/>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F484" s="5" t="n">
+        <v>-0.296</v>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
         <is>
           <t>Deficit, end of year $</t>
         </is>
       </c>
-      <c r="D469" t="inlineStr"/>
-      <c r="E469" s="5" t="n">
+      <c r="D485" t="inlineStr"/>
+      <c r="E485" s="5" t="n">
         <v>-20.394572</v>
       </c>
-      <c r="F469" s="5" t="n">
+      <c r="F485" s="5" t="n">
         <v>-22.547313</v>
       </c>
-      <c r="G469" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H469" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I469" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J469" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K469" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L469" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M469" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N469" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O469" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P469" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q469" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R469" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S469" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T469" t="inlineStr">
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H485" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I485" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J485" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L485" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M485" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N485" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O485" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P485" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q485" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R485" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S485" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T485" t="inlineStr">
         <is>
           <t>-</t>
         </is>
